--- a/artfynd/A 25852-2026 artfynd.xlsx
+++ b/artfynd/A 25852-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>56218510</v>
+        <v>56218508</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>535506.8552651597</v>
+        <v>535446</v>
       </c>
       <c r="R2" t="n">
-        <v>6980045.226191216</v>
+        <v>6980194</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2013-05-16</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2013-05-16</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,12 +779,7 @@
         <v>56218505</v>
       </c>
       <c r="B3" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -831,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>535396.837960235</v>
+        <v>535397</v>
       </c>
       <c r="R3" t="n">
-        <v>6980269.812728938</v>
+        <v>6980270</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,19 +844,9 @@
           <t>2013-05-16</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2013-05-16</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,15 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>56218508</v>
+        <v>56218503</v>
       </c>
       <c r="B4" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -923,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>53</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>535445.974956965</v>
+        <v>535494</v>
       </c>
       <c r="R4" t="n">
-        <v>6980194.328561445</v>
+        <v>6980290</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,19 +945,9 @@
           <t>2013-05-16</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2013-05-16</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,37 +978,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>56218506</v>
+        <v>56218502</v>
       </c>
       <c r="B5" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>535402.8419521123</v>
+        <v>535499</v>
       </c>
       <c r="R5" t="n">
-        <v>6980262.594818447</v>
+        <v>6980290</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,19 +1046,9 @@
           <t>2013-05-16</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2013-05-16</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,6 +1072,410 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>56218504</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Ö om Störbodknulen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>535525</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6980233</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2013-05-16</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2013-05-16</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Sebastian Acker</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Sebastian Acker</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>56218506</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ö om Störbodknulen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>535403</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6980263</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2013-05-16</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2013-05-16</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Sebastian Acker</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Sebastian Acker</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>56218500</v>
+      </c>
+      <c r="B8" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Ö om Störbodknulen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>535426</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6980344</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2013-06-24</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2013-06-24</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Sebastian Acker</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Sebastian Acker</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>56218510</v>
+      </c>
+      <c r="B9" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Ö om Störbodknulen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>535507</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6980045</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2013-05-16</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2013-05-16</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Sebastian Acker</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Sebastian Acker</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
         </is>

--- a/artfynd/A 25852-2026 artfynd.xlsx
+++ b/artfynd/A 25852-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56218508</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56218505</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56218503</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56218502</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56218504</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56218506</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56218500</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1480,8 +1520,23 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56218510</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>